--- a/web-app/public/upload-tagihan-example.xlsx
+++ b/web-app/public/upload-tagihan-example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SyrelGroup\Hasamitra\apps-hmjb\web-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7852FCDF-DB68-4224-A122-175D5B937C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2A2C4A-2847-44FE-9A2F-DD0019920CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>INSTANSI</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>BELUMBAYAR</t>
+  </si>
+  <si>
+    <t>PERIODE</t>
   </si>
 </sst>
 </file>
@@ -156,7 +159,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -173,6 +176,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -701,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -721,9 +727,10 @@
     <col min="15" max="15" width="13.5703125" style="5" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="11.140625" customWidth="1"/>
+    <col min="18" max="18" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -778,8 +785,11 @@
       <c r="R1" t="s">
         <v>19</v>
       </c>
+      <c r="S1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:19">
       <c r="A2" s="2" t="s">
         <v>20</v>
       </c>
@@ -834,8 +844,11 @@
       <c r="R2" t="s">
         <v>24</v>
       </c>
+      <c r="S2" s="6">
+        <v>46208</v>
+      </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:19">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -890,8 +903,11 @@
       <c r="R3" t="s">
         <v>25</v>
       </c>
+      <c r="S3" s="6">
+        <v>46208</v>
+      </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:19">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -945,6 +961,9 @@
       </c>
       <c r="R4" t="s">
         <v>26</v>
+      </c>
+      <c r="S4" s="6">
+        <v>46208</v>
       </c>
     </row>
   </sheetData>
